--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/130.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/130.xlsx
@@ -426,13 +426,13 @@
         <v>-10.80136807384815</v>
       </c>
       <c r="E2">
-        <v>-25.07225164114713</v>
+        <v>-30.64969004676923</v>
       </c>
       <c r="F2">
-        <v>-2.707312739814395</v>
+        <v>-3.788733130290705</v>
       </c>
       <c r="G2">
-        <v>-14.10068721917904</v>
+        <v>-17.29209450085571</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.09020071069532</v>
       </c>
       <c r="E3">
-        <v>-25.4179010052046</v>
+        <v>-30.84567108063619</v>
       </c>
       <c r="F3">
-        <v>-2.62991340316642</v>
+        <v>-3.622452456424551</v>
       </c>
       <c r="G3">
-        <v>-14.18071965759092</v>
+        <v>-16.7490359211392</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.27952584591625</v>
       </c>
       <c r="E4">
-        <v>-25.35798929408312</v>
+        <v>-30.59000928782215</v>
       </c>
       <c r="F4">
-        <v>-2.640898383294944</v>
+        <v>-3.714339110580087</v>
       </c>
       <c r="G4">
-        <v>-13.64392297476195</v>
+        <v>-16.93324957239918</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.3278868402592</v>
       </c>
       <c r="E5">
-        <v>-25.98265605564918</v>
+        <v>-31.61025183938024</v>
       </c>
       <c r="F5">
-        <v>-2.599055060677333</v>
+        <v>-3.702968111241858</v>
       </c>
       <c r="G5">
-        <v>-13.82440564119917</v>
+        <v>-16.75880203048005</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.23981532954091</v>
       </c>
       <c r="E6">
-        <v>-26.11786723257021</v>
+        <v>-31.81103758416933</v>
       </c>
       <c r="F6">
-        <v>-2.655712077559208</v>
+        <v>-3.717912687555764</v>
       </c>
       <c r="G6">
-        <v>-13.28597520414656</v>
+        <v>-16.72525130671231</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.01203263500265</v>
       </c>
       <c r="E7">
-        <v>-26.61227696777964</v>
+        <v>-32.16597258417952</v>
       </c>
       <c r="F7">
-        <v>-2.796264488261811</v>
+        <v>-3.717668319171938</v>
       </c>
       <c r="G7">
-        <v>-12.94821017441134</v>
+        <v>-16.34859895380004</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.66140798105356</v>
       </c>
       <c r="E8">
-        <v>-26.58357097104502</v>
+        <v>-32.03938588600611</v>
       </c>
       <c r="F8">
-        <v>-2.737485194093964</v>
+        <v>-3.588344428614282</v>
       </c>
       <c r="G8">
-        <v>-12.92321886613538</v>
+        <v>-15.94202423503106</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.19743180383929</v>
       </c>
       <c r="E9">
-        <v>-27.57340934811561</v>
+        <v>-32.63079100598583</v>
       </c>
       <c r="F9">
-        <v>-2.563200006014559</v>
+        <v>-3.7202611091427</v>
       </c>
       <c r="G9">
-        <v>-12.80918381448965</v>
+        <v>-15.9152617848916</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.634842129502243</v>
       </c>
       <c r="E10">
-        <v>-27.82509740498792</v>
+        <v>-33.24009265524388</v>
       </c>
       <c r="F10">
-        <v>-2.670265664458992</v>
+        <v>-3.639174709184865</v>
       </c>
       <c r="G10">
-        <v>-12.34246972545427</v>
+        <v>-15.70107114377352</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.000031599265791</v>
       </c>
       <c r="E11">
-        <v>-28.30005734433441</v>
+        <v>-33.5592708244895</v>
       </c>
       <c r="F11">
-        <v>-2.561276536905259</v>
+        <v>-3.687751002052431</v>
       </c>
       <c r="G11">
-        <v>-12.22096939361748</v>
+        <v>-15.51679955796661</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.313700609008361</v>
       </c>
       <c r="E12">
-        <v>-28.20814743587474</v>
+        <v>-33.88240235154382</v>
       </c>
       <c r="F12">
-        <v>-2.551184536836952</v>
+        <v>-3.576001754312569</v>
       </c>
       <c r="G12">
-        <v>-11.99863977629111</v>
+        <v>-15.36158131981234</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.592778007367379</v>
       </c>
       <c r="E13">
-        <v>-29.29533441868822</v>
+        <v>-34.25428516552772</v>
       </c>
       <c r="F13">
-        <v>-2.504498578382575</v>
+        <v>-3.603468760654595</v>
       </c>
       <c r="G13">
-        <v>-12.11379710287465</v>
+        <v>-15.07395450226938</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.867460753799153</v>
       </c>
       <c r="E14">
-        <v>-29.63140832445646</v>
+        <v>-35.2075130944833</v>
       </c>
       <c r="F14">
-        <v>-2.339314662957729</v>
+        <v>-3.568923354855647</v>
       </c>
       <c r="G14">
-        <v>-11.53477275641951</v>
+        <v>-14.72669151738199</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.153456829945501</v>
       </c>
       <c r="E15">
-        <v>-30.54380073904788</v>
+        <v>-35.61944120411703</v>
       </c>
       <c r="F15">
-        <v>-2.224385312758519</v>
+        <v>-3.462719198510126</v>
       </c>
       <c r="G15">
-        <v>-11.42801759441463</v>
+        <v>-14.32859510573909</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.45803338734819</v>
       </c>
       <c r="E16">
-        <v>-30.7978594520632</v>
+        <v>-36.09592950344111</v>
       </c>
       <c r="F16">
-        <v>-2.175802392951731</v>
+        <v>-3.254548813451804</v>
       </c>
       <c r="G16">
-        <v>-10.98676491112179</v>
+        <v>-14.33086117416072</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.799530101644792</v>
       </c>
       <c r="E17">
-        <v>-32.02669257336261</v>
+        <v>-36.65042076754731</v>
       </c>
       <c r="F17">
-        <v>-2.062292036113518</v>
+        <v>-3.20243704850909</v>
       </c>
       <c r="G17">
-        <v>-10.70108138381038</v>
+        <v>-14.32674451078264</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.182315187533782</v>
       </c>
       <c r="E18">
-        <v>-32.71502967947652</v>
+        <v>-37.03275982801492</v>
       </c>
       <c r="F18">
-        <v>-1.83007497371933</v>
+        <v>-3.087862239558279</v>
       </c>
       <c r="G18">
-        <v>-10.52062685701025</v>
+        <v>-13.9450204021042</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.602500828469997</v>
       </c>
       <c r="E19">
-        <v>-33.3637969797114</v>
+        <v>-37.73885760918691</v>
       </c>
       <c r="F19">
-        <v>-1.77972514624237</v>
+        <v>-2.918852923467305</v>
       </c>
       <c r="G19">
-        <v>-10.3729632837766</v>
+        <v>-13.88634594823893</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.066472776042129</v>
       </c>
       <c r="E20">
-        <v>-33.49536273505625</v>
+        <v>-38.6825847996744</v>
       </c>
       <c r="F20">
-        <v>-1.596125795085888</v>
+        <v>-2.869632989127763</v>
       </c>
       <c r="G20">
-        <v>-10.0916728503958</v>
+        <v>-13.83844566483122</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.569491249474027</v>
       </c>
       <c r="E21">
-        <v>-34.75427850918861</v>
+        <v>-39.01374531114433</v>
       </c>
       <c r="F21">
-        <v>-1.517695141021428</v>
+        <v>-2.623225164756217</v>
       </c>
       <c r="G21">
-        <v>-10.23199363362335</v>
+        <v>-13.53796068841373</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.103239610292526</v>
       </c>
       <c r="E22">
-        <v>-34.86845039587</v>
+        <v>-39.40748933340025</v>
       </c>
       <c r="F22">
-        <v>-1.325385506624508</v>
+        <v>-2.496764940310039</v>
       </c>
       <c r="G22">
-        <v>-9.957963226610179</v>
+        <v>-13.54261697071471</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.672990827804989</v>
       </c>
       <c r="E23">
-        <v>-35.16084943407127</v>
+        <v>-39.95237796837318</v>
       </c>
       <c r="F23">
-        <v>-1.091820690465965</v>
+        <v>-2.379117716662245</v>
       </c>
       <c r="G23">
-        <v>-9.979279829337546</v>
+        <v>-13.32565209243473</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.281077072727534</v>
       </c>
       <c r="E24">
-        <v>-35.51844264832395</v>
+        <v>-40.11703328329208</v>
       </c>
       <c r="F24">
-        <v>-1.20098460354169</v>
+        <v>-2.202420322705888</v>
       </c>
       <c r="G24">
-        <v>-10.13401472784308</v>
+        <v>-13.3392385713279</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.9316858894178214</v>
       </c>
       <c r="E25">
-        <v>-36.07323732018867</v>
+        <v>-40.0593676952784</v>
       </c>
       <c r="F25">
-        <v>-0.8659431238054017</v>
+        <v>-2.115035845384568</v>
       </c>
       <c r="G25">
-        <v>-9.783921226519615</v>
+        <v>-13.59637857499971</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.6398115707558915</v>
       </c>
       <c r="E26">
-        <v>-36.22821528615317</v>
+        <v>-40.2060177975428</v>
       </c>
       <c r="F26">
-        <v>-0.908080516851007</v>
+        <v>-2.214811042316963</v>
       </c>
       <c r="G26">
-        <v>-10.11463148371065</v>
+        <v>-13.59999534600136</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.4169877493851243</v>
       </c>
       <c r="E27">
-        <v>-36.14330187003535</v>
+        <v>-39.99080207032826</v>
       </c>
       <c r="F27">
-        <v>-0.8426610295823188</v>
+        <v>-2.005546383919543</v>
       </c>
       <c r="G27">
-        <v>-10.00334749540805</v>
+        <v>-13.62574973502412</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.2747668857910099</v>
       </c>
       <c r="E28">
-        <v>-35.91395051120587</v>
+        <v>-40.16413394144586</v>
       </c>
       <c r="F28">
-        <v>-0.8229864753984277</v>
+        <v>-2.045393341096408</v>
       </c>
       <c r="G28">
-        <v>-10.1174686212378</v>
+        <v>-13.92850905622709</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.2267564528217257</v>
       </c>
       <c r="E29">
-        <v>-36.00451319864827</v>
+        <v>-40.41421439004544</v>
       </c>
       <c r="F29">
-        <v>-0.6669377956916541</v>
+        <v>-2.088813046881547</v>
       </c>
       <c r="G29">
-        <v>-10.16707383559824</v>
+        <v>-13.51308524923164</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.2782988644097028</v>
       </c>
       <c r="E30">
-        <v>-35.76120508292715</v>
+        <v>-40.60356120949116</v>
       </c>
       <c r="F30">
-        <v>-0.5705191434754029</v>
+        <v>-1.804147902379108</v>
       </c>
       <c r="G30">
-        <v>-10.20000383207737</v>
+        <v>-13.82261132551688</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.4322899943101864</v>
       </c>
       <c r="E31">
-        <v>-35.36587609476854</v>
+        <v>-39.83875855552073</v>
       </c>
       <c r="F31">
-        <v>-0.6916446818475521</v>
+        <v>-1.910627076702359</v>
       </c>
       <c r="G31">
-        <v>-10.08095661448518</v>
+        <v>-14.16264738949204</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.6860834607900712</v>
       </c>
       <c r="E32">
-        <v>-34.85570727001241</v>
+        <v>-39.55094686148924</v>
       </c>
       <c r="F32">
-        <v>-0.8733387879775957</v>
+        <v>-2.138686563101897</v>
       </c>
       <c r="G32">
-        <v>-10.55240809418725</v>
+        <v>-13.84919997201554</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.025519903624436</v>
       </c>
       <c r="E33">
-        <v>-35.19054263813956</v>
+        <v>-39.36445298066835</v>
       </c>
       <c r="F33">
-        <v>-0.7906436985235239</v>
+        <v>-2.103619285839185</v>
       </c>
       <c r="G33">
-        <v>-10.40442339803629</v>
+        <v>-14.1996592886211</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.437810739382802</v>
       </c>
       <c r="E34">
-        <v>-34.6154105895064</v>
+        <v>-39.01445401732652</v>
       </c>
       <c r="F34">
-        <v>-0.806339604071769</v>
+        <v>-1.854340340049536</v>
       </c>
       <c r="G34">
-        <v>-11.04751011122188</v>
+        <v>-14.05198412847806</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.907665552829846</v>
       </c>
       <c r="E35">
-        <v>-33.63970784405075</v>
+        <v>-38.54049939920974</v>
       </c>
       <c r="F35">
-        <v>-0.8395206887583059</v>
+        <v>-2.111548418618782</v>
       </c>
       <c r="G35">
-        <v>-11.08251581975413</v>
+        <v>-14.37396116653649</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.414345108067356</v>
       </c>
       <c r="E36">
-        <v>-33.65736436420665</v>
+        <v>-38.41894609989585</v>
       </c>
       <c r="F36">
-        <v>-0.7534889354057577</v>
+        <v>-1.984065160430146</v>
       </c>
       <c r="G36">
-        <v>-11.21261363835641</v>
+        <v>-14.34747845749509</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.946703516517408</v>
       </c>
       <c r="E37">
-        <v>-33.50551104530744</v>
+        <v>-37.89287553866178</v>
       </c>
       <c r="F37">
-        <v>-0.720281342962331</v>
+        <v>-1.921868850725751</v>
       </c>
       <c r="G37">
-        <v>-10.82566714408978</v>
+        <v>-14.19268396916985</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.492670336604681</v>
       </c>
       <c r="E38">
-        <v>-32.65407415509627</v>
+        <v>-37.40659667853313</v>
       </c>
       <c r="F38">
-        <v>-0.7008668961429191</v>
+        <v>-2.041258959389035</v>
       </c>
       <c r="G38">
-        <v>-10.78126610731707</v>
+        <v>-14.59355627324743</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.034773445670133</v>
       </c>
       <c r="E39">
-        <v>-32.88914724083444</v>
+        <v>-36.90154502940567</v>
       </c>
       <c r="F39">
-        <v>-0.6692704782979375</v>
+        <v>-2.058442612792708</v>
       </c>
       <c r="G39">
-        <v>-10.97349293405485</v>
+        <v>-14.51574686616517</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.568156447634888</v>
       </c>
       <c r="E40">
-        <v>-32.03817451920906</v>
+        <v>-36.36725528784768</v>
       </c>
       <c r="F40">
-        <v>-0.662083562711249</v>
+        <v>-2.123128994909919</v>
       </c>
       <c r="G40">
-        <v>-11.30780506479261</v>
+        <v>-14.23864096234601</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.087014866914082</v>
       </c>
       <c r="E41">
-        <v>-31.2944292693743</v>
+        <v>-35.62038312671063</v>
       </c>
       <c r="F41">
-        <v>-0.6785457081070836</v>
+        <v>-1.871034428318154</v>
       </c>
       <c r="G41">
-        <v>-11.12219601858783</v>
+        <v>-14.57067212720722</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.579172210306949</v>
       </c>
       <c r="E42">
-        <v>-30.73758772725812</v>
+        <v>-35.86787102394082</v>
       </c>
       <c r="F42">
-        <v>-0.6131021981837143</v>
+        <v>-1.893766486585778</v>
       </c>
       <c r="G42">
-        <v>-11.10905315279693</v>
+        <v>-14.61411641631907</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.046284590182875</v>
       </c>
       <c r="E43">
-        <v>-30.23998315363627</v>
+        <v>-35.13865764719667</v>
       </c>
       <c r="F43">
-        <v>-0.478181029085342</v>
+        <v>-1.79863014710906</v>
       </c>
       <c r="G43">
-        <v>-11.25520711726467</v>
+        <v>-14.59531913874709</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.488138762017444</v>
       </c>
       <c r="E44">
-        <v>-30.01980648314633</v>
+        <v>-34.39520674817241</v>
       </c>
       <c r="F44">
-        <v>-0.5295381513241058</v>
+        <v>-1.624194196162346</v>
       </c>
       <c r="G44">
-        <v>-11.2860713333273</v>
+        <v>-14.35672481118628</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.896454596369907</v>
       </c>
       <c r="E45">
-        <v>-29.05313804333598</v>
+        <v>-33.89568889428233</v>
       </c>
       <c r="F45">
-        <v>-0.4412350145530812</v>
+        <v>-1.783701309775808</v>
       </c>
       <c r="G45">
-        <v>-11.18722506461574</v>
+        <v>-14.5400528915145</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.27424639856519</v>
       </c>
       <c r="E46">
-        <v>-28.5326624117384</v>
+        <v>-33.42662049961982</v>
       </c>
       <c r="F46">
-        <v>-0.3867557755731661</v>
+        <v>-1.664663257258713</v>
       </c>
       <c r="G46">
-        <v>-11.20237081045791</v>
+        <v>-14.77249953600889</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.621879295447541</v>
       </c>
       <c r="E47">
-        <v>-28.26325443607407</v>
+        <v>-32.99766985619126</v>
       </c>
       <c r="F47">
-        <v>-0.4034639460876321</v>
+        <v>-1.657335519213549</v>
       </c>
       <c r="G47">
-        <v>-10.86695295751003</v>
+        <v>-14.5297604054329</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.932254010813216</v>
       </c>
       <c r="E48">
-        <v>-27.81808732722405</v>
+        <v>-32.53284464167393</v>
       </c>
       <c r="F48">
-        <v>-0.3744951096443306</v>
+        <v>-1.684000665909665</v>
       </c>
       <c r="G48">
-        <v>-11.11063228301916</v>
+        <v>-14.60229776874387</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.206610204814288</v>
       </c>
       <c r="E49">
-        <v>-27.44610941528599</v>
+        <v>-32.47127098059164</v>
       </c>
       <c r="F49">
-        <v>-0.2732213960802715</v>
+        <v>-1.45854888009414</v>
       </c>
       <c r="G49">
-        <v>-10.99399183203402</v>
+        <v>-14.79547472205143</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.44556135815774</v>
       </c>
       <c r="E50">
-        <v>-26.71217963286286</v>
+        <v>-31.88279804753188</v>
       </c>
       <c r="F50">
-        <v>-0.3597783343661946</v>
+        <v>-1.563239609194747</v>
       </c>
       <c r="G50">
-        <v>-11.10805005749853</v>
+        <v>-14.73484373577245</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.644835284912928</v>
       </c>
       <c r="E51">
-        <v>-26.1906624522435</v>
+        <v>-31.12790369469024</v>
       </c>
       <c r="F51">
-        <v>-0.1052251733229206</v>
+        <v>-1.553290916687125</v>
       </c>
       <c r="G51">
-        <v>-11.29608242303805</v>
+        <v>-14.59826883482258</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.806111460467562</v>
       </c>
       <c r="E52">
-        <v>-25.57413335846923</v>
+        <v>-30.67065008871374</v>
       </c>
       <c r="F52">
-        <v>-0.3261689837324103</v>
+        <v>-1.544401706087684</v>
       </c>
       <c r="G52">
-        <v>-11.14361855877246</v>
+        <v>-14.88118309079039</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.931991742083708</v>
       </c>
       <c r="E53">
-        <v>-25.05192784980071</v>
+        <v>-30.67906625765699</v>
       </c>
       <c r="F53">
-        <v>-0.2187115075064528</v>
+        <v>-1.460609858192305</v>
       </c>
       <c r="G53">
-        <v>-11.46650930739973</v>
+        <v>-15.15351022212361</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.022873452095844</v>
       </c>
       <c r="E54">
-        <v>-24.73748872860411</v>
+        <v>-29.73450129947808</v>
       </c>
       <c r="F54">
-        <v>-0.230568758510125</v>
+        <v>-1.492527682589573</v>
       </c>
       <c r="G54">
-        <v>-11.15159035243102</v>
+        <v>-15.05267266027018</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.082360739325745</v>
       </c>
       <c r="E55">
-        <v>-24.4545134448128</v>
+        <v>-29.75619948268583</v>
       </c>
       <c r="F55">
-        <v>-0.292162845112685</v>
+        <v>-1.526470036919283</v>
       </c>
       <c r="G55">
-        <v>-11.35802273007782</v>
+        <v>-15.1574464607698</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.115673969158649</v>
       </c>
       <c r="E56">
-        <v>-23.85264754987536</v>
+        <v>-29.15505587935261</v>
       </c>
       <c r="F56">
-        <v>-0.1176722219173859</v>
+        <v>-1.385115766570769</v>
       </c>
       <c r="G56">
-        <v>-11.30843075789954</v>
+        <v>-15.05264121008755</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.127927804246543</v>
       </c>
       <c r="E57">
-        <v>-23.23204282949418</v>
+        <v>-29.03441733178828</v>
       </c>
       <c r="F57">
-        <v>-0.1092319864502618</v>
+        <v>-1.453767543445181</v>
       </c>
       <c r="G57">
-        <v>-11.53201507198529</v>
+        <v>-14.973015968777</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.12436427753585</v>
       </c>
       <c r="E58">
-        <v>-23.3849105265711</v>
+        <v>-28.34924562900573</v>
       </c>
       <c r="F58">
-        <v>-0.2523523361015436</v>
+        <v>-1.622284809298893</v>
       </c>
       <c r="G58">
-        <v>-11.30016432568797</v>
+        <v>-15.04162040398732</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.111551132937288</v>
       </c>
       <c r="E59">
-        <v>-22.78340690955427</v>
+        <v>-28.58069593553776</v>
       </c>
       <c r="F59">
-        <v>-0.3041344108179435</v>
+        <v>-1.473727884383038</v>
       </c>
       <c r="G59">
-        <v>-11.4918978811404</v>
+        <v>-14.74610124587874</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.097435331669233</v>
       </c>
       <c r="E60">
-        <v>-22.59403971197552</v>
+        <v>-28.06504312875834</v>
       </c>
       <c r="F60">
-        <v>-0.3915379405895277</v>
+        <v>-1.579131837817456</v>
       </c>
       <c r="G60">
-        <v>-11.36988110419949</v>
+        <v>-15.30315350158974</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.086011401268154</v>
       </c>
       <c r="E61">
-        <v>-22.40393890160753</v>
+        <v>-28.23550394735507</v>
       </c>
       <c r="F61">
-        <v>-0.295220349196418</v>
+        <v>-1.590743892069899</v>
       </c>
       <c r="G61">
-        <v>-11.3797365982699</v>
+        <v>-15.11668205827198</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.081369854317412</v>
       </c>
       <c r="E62">
-        <v>-22.10370560337299</v>
+        <v>-27.96121427671048</v>
       </c>
       <c r="F62">
-        <v>-0.4238094778677908</v>
+        <v>-1.507235345826278</v>
       </c>
       <c r="G62">
-        <v>-11.47908606990343</v>
+        <v>-15.3139276720473</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.090644495561266</v>
       </c>
       <c r="E63">
-        <v>-22.20058777629309</v>
+        <v>-27.81780656183557</v>
       </c>
       <c r="F63">
-        <v>-0.4895371178103204</v>
+        <v>-1.758164399482304</v>
       </c>
       <c r="G63">
-        <v>-11.64309711701</v>
+        <v>-14.98929226592083</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.113073638212818</v>
       </c>
       <c r="E64">
-        <v>-22.17784577982657</v>
+        <v>-27.67206215437271</v>
       </c>
       <c r="F64">
-        <v>-0.4813106011331185</v>
+        <v>-1.587316107757115</v>
       </c>
       <c r="G64">
-        <v>-11.59423015430482</v>
+        <v>-15.30043885424754</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.146643053887297</v>
       </c>
       <c r="E65">
-        <v>-21.6968765554719</v>
+        <v>-27.44772155203272</v>
       </c>
       <c r="F65">
-        <v>-0.6893998061859655</v>
+        <v>-1.825520609738738</v>
       </c>
       <c r="G65">
-        <v>-11.39096265819357</v>
+        <v>-15.39288749370446</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.193082536827774</v>
       </c>
       <c r="E66">
-        <v>-21.55876715518597</v>
+        <v>-27.53236778818409</v>
       </c>
       <c r="F66">
-        <v>-0.4567677317229747</v>
+        <v>-1.848362840870934</v>
       </c>
       <c r="G66">
-        <v>-11.50175668575636</v>
+        <v>-15.17654665325862</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.24393443709169</v>
       </c>
       <c r="E67">
-        <v>-21.60848074284218</v>
+        <v>-26.96120947549266</v>
       </c>
       <c r="F67">
-        <v>-0.8161052273833723</v>
+        <v>-1.96812902833509</v>
       </c>
       <c r="G67">
-        <v>-11.52016662950024</v>
+        <v>-15.11186521451234</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.29052960300988</v>
       </c>
       <c r="E68">
-        <v>-21.74946119564897</v>
+        <v>-27.39088920323646</v>
       </c>
       <c r="F68">
-        <v>-0.6863853772071781</v>
+        <v>-2.104211568532187</v>
       </c>
       <c r="G68">
-        <v>-11.47492471416056</v>
+        <v>-14.74935385687107</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.329048961194705</v>
       </c>
       <c r="E69">
-        <v>-21.09097579019362</v>
+        <v>-27.2248391183232</v>
       </c>
       <c r="F69">
-        <v>-0.9649992978321666</v>
+        <v>-2.039009113523032</v>
       </c>
       <c r="G69">
-        <v>-11.24461668208454</v>
+        <v>-14.98503821490286</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.347524571329242</v>
       </c>
       <c r="E70">
-        <v>-21.21372007817153</v>
+        <v>-27.31927591527916</v>
       </c>
       <c r="F70">
-        <v>-0.9146743213772911</v>
+        <v>-2.241666713515723</v>
       </c>
       <c r="G70">
-        <v>-11.26637027682309</v>
+        <v>-15.07645230887876</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.336437521592547</v>
       </c>
       <c r="E71">
-        <v>-20.9379314826304</v>
+        <v>-27.11918076277624</v>
       </c>
       <c r="F71">
-        <v>-1.162224464397298</v>
+        <v>-2.271873130858807</v>
       </c>
       <c r="G71">
-        <v>-11.50013120789657</v>
+        <v>-14.99575279554072</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.294058410828256</v>
       </c>
       <c r="E72">
-        <v>-21.69385153483478</v>
+        <v>-27.49321007343977</v>
       </c>
       <c r="F72">
-        <v>-1.347994966516518</v>
+        <v>-2.328159039144227</v>
       </c>
       <c r="G72">
-        <v>-11.01634794606072</v>
+        <v>-14.52509750204084</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.213084020361462</v>
       </c>
       <c r="E73">
-        <v>-21.26644057256883</v>
+        <v>-26.80526694456453</v>
       </c>
       <c r="F73">
-        <v>-1.221396404714072</v>
+        <v>-2.54722162718196</v>
       </c>
       <c r="G73">
-        <v>-11.17709810581111</v>
+        <v>-14.88336805084631</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.089965081422726</v>
       </c>
       <c r="E74">
-        <v>-21.2877379858269</v>
+        <v>-27.30844833392682</v>
       </c>
       <c r="F74">
-        <v>-1.414260216903465</v>
+        <v>-2.531802396346249</v>
       </c>
       <c r="G74">
-        <v>-10.9674445673546</v>
+        <v>-14.45830724578604</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.93005061832493</v>
       </c>
       <c r="E75">
-        <v>-21.52009398716047</v>
+        <v>-27.62388824787911</v>
       </c>
       <c r="F75">
-        <v>-1.52554889236737</v>
+        <v>-2.474776755970129</v>
       </c>
       <c r="G75">
-        <v>-11.06990926234059</v>
+        <v>-14.63826850130082</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.733028326023197</v>
       </c>
       <c r="E76">
-        <v>-21.70593350348724</v>
+        <v>-27.25625767098842</v>
       </c>
       <c r="F76">
-        <v>-1.753164373839007</v>
+        <v>-2.71417327864438</v>
       </c>
       <c r="G76">
-        <v>-10.59087663335358</v>
+        <v>-14.57691416082151</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.500375931920955</v>
       </c>
       <c r="E77">
-        <v>-21.91919745840447</v>
+        <v>-27.5819636355161</v>
       </c>
       <c r="F77">
-        <v>-1.893862577204503</v>
+        <v>-2.80464673801074</v>
       </c>
       <c r="G77">
-        <v>-11.01251433432624</v>
+        <v>-14.37724688298422</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.240826213512008</v>
       </c>
       <c r="E78">
-        <v>-22.36673748763452</v>
+        <v>-27.98125730266842</v>
       </c>
       <c r="F78">
-        <v>-1.826159281006296</v>
+        <v>-2.848377081571928</v>
       </c>
       <c r="G78">
-        <v>-10.30615978533964</v>
+        <v>-14.31534961303647</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.955940538207006</v>
       </c>
       <c r="E79">
-        <v>-21.95254061252295</v>
+        <v>-28.02853457130851</v>
       </c>
       <c r="F79">
-        <v>-1.749661208092568</v>
+        <v>-3.049596635753359</v>
       </c>
       <c r="G79">
-        <v>-10.82206527054305</v>
+        <v>-14.16222198439025</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.64683823297703</v>
       </c>
       <c r="E80">
-        <v>-23.00370358460541</v>
+        <v>-28.35291369295194</v>
       </c>
       <c r="F80">
-        <v>-1.955334065431448</v>
+        <v>-2.992590047827503</v>
       </c>
       <c r="G80">
-        <v>-10.02760055202875</v>
+        <v>-14.21584123521705</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.321601032762711</v>
       </c>
       <c r="E81">
-        <v>-22.9682728039694</v>
+        <v>-28.74936800690146</v>
       </c>
       <c r="F81">
-        <v>-2.038440853484711</v>
+        <v>-3.06395389957868</v>
       </c>
       <c r="G81">
-        <v>-10.10253806085569</v>
+        <v>-13.77529038757854</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.982370048885171</v>
       </c>
       <c r="E82">
-        <v>-23.40996204478154</v>
+        <v>-29.00423505252715</v>
       </c>
       <c r="F82">
-        <v>-1.842603202319269</v>
+        <v>-2.997479900606228</v>
       </c>
       <c r="G82">
-        <v>-9.935944788228486</v>
+        <v>-14.31388304136257</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.630991726826013</v>
       </c>
       <c r="E83">
-        <v>-23.73111236445751</v>
+        <v>-29.28132332010849</v>
       </c>
       <c r="F83">
-        <v>-1.957123339021495</v>
+        <v>-3.233643305307353</v>
       </c>
       <c r="G83">
-        <v>-9.808164351503697</v>
+        <v>-14.06323501749327</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.276640010710805</v>
       </c>
       <c r="E84">
-        <v>-24.75528563145426</v>
+        <v>-30.05648032989745</v>
       </c>
       <c r="F84">
-        <v>-2.304157093648112</v>
+        <v>-3.145396497519719</v>
       </c>
       <c r="G84">
-        <v>-9.925159030861542</v>
+        <v>-14.04638930651669</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.92405687915681</v>
       </c>
       <c r="E85">
-        <v>-25.61811389803172</v>
+        <v>-30.90706360275817</v>
       </c>
       <c r="F85">
-        <v>-2.13139941505947</v>
+        <v>-3.154914438977885</v>
       </c>
       <c r="G85">
-        <v>-9.811670219229786</v>
+        <v>-13.7242897782733</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.577469960273438</v>
       </c>
       <c r="E86">
-        <v>-25.91490555602043</v>
+        <v>-31.06467714059514</v>
       </c>
       <c r="F86">
-        <v>-2.251526770711245</v>
+        <v>-3.395760604607036</v>
       </c>
       <c r="G86">
-        <v>-9.456303018862259</v>
+        <v>-13.79853207253699</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.247240673650107</v>
       </c>
       <c r="E87">
-        <v>-27.49826837890634</v>
+        <v>-32.33409671018829</v>
       </c>
       <c r="F87">
-        <v>-2.170519894024079</v>
+        <v>-3.43774392131572</v>
       </c>
       <c r="G87">
-        <v>-10.1887943248814</v>
+        <v>-13.83889589902456</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.939780067732758</v>
       </c>
       <c r="E88">
-        <v>-27.97629409515602</v>
+        <v>-32.74344358963765</v>
       </c>
       <c r="F88">
-        <v>-2.35388813067518</v>
+        <v>-3.359043219477948</v>
       </c>
       <c r="G88">
-        <v>-9.581458192974406</v>
+        <v>-13.49226688360794</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.661310727414731</v>
       </c>
       <c r="E89">
-        <v>-29.42457706686713</v>
+        <v>-33.51561859929256</v>
       </c>
       <c r="F89">
-        <v>-2.347927198844635</v>
+        <v>-3.597145832269026</v>
       </c>
       <c r="G89">
-        <v>-9.609799773336107</v>
+        <v>-13.58075280005435</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.421751018300916</v>
       </c>
       <c r="E90">
-        <v>-30.16042239379551</v>
+        <v>-34.72592346918958</v>
       </c>
       <c r="F90">
-        <v>-2.429030994517929</v>
+        <v>-3.71365653584018</v>
       </c>
       <c r="G90">
-        <v>-9.763359428175201</v>
+        <v>-13.88328038306956</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.225640719080756</v>
       </c>
       <c r="E91">
-        <v>-31.41160127008576</v>
+        <v>-35.71993709929525</v>
       </c>
       <c r="F91">
-        <v>-2.516823028601426</v>
+        <v>-3.627361361653541</v>
       </c>
       <c r="G91">
-        <v>-9.852893132284791</v>
+        <v>-13.66263086760437</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.075419960028996</v>
       </c>
       <c r="E92">
-        <v>-32.49641759675623</v>
+        <v>-36.89641426835497</v>
       </c>
       <c r="F92">
-        <v>-2.866944108538276</v>
+        <v>-3.729962119796885</v>
       </c>
       <c r="G92">
-        <v>-9.781782614101246</v>
+        <v>-14.1791835644607</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.974026634507004</v>
       </c>
       <c r="E93">
-        <v>-33.69491220644125</v>
+        <v>-37.76580202953255</v>
       </c>
       <c r="F93">
-        <v>-2.96996484895484</v>
+        <v>-3.979066280064544</v>
       </c>
       <c r="G93">
-        <v>-10.02245927480626</v>
+        <v>-14.33782490670258</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.918582341648782</v>
       </c>
       <c r="E94">
-        <v>-35.35199632193503</v>
+        <v>-38.88162481773354</v>
       </c>
       <c r="F94">
-        <v>-2.837704395954259</v>
+        <v>-4.08615347606145</v>
       </c>
       <c r="G94">
-        <v>-10.50686160865796</v>
+        <v>-14.20441654256103</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.904383603499751</v>
       </c>
       <c r="E95">
-        <v>-36.94709694944882</v>
+        <v>-40.3020146537944</v>
       </c>
       <c r="F95">
-        <v>-2.960200054010639</v>
+        <v>-4.108552530633149</v>
       </c>
       <c r="G95">
-        <v>-10.42067817663411</v>
+        <v>-14.09490369612194</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.925875213060196</v>
       </c>
       <c r="E96">
-        <v>-38.46194396059868</v>
+        <v>-41.9385644039004</v>
       </c>
       <c r="F96">
-        <v>-3.208664714643337</v>
+        <v>-4.373658264020686</v>
       </c>
       <c r="G96">
-        <v>-10.51470760158603</v>
+        <v>-14.32534911583783</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.97286073288151</v>
       </c>
       <c r="E97">
-        <v>-40.03928617729139</v>
+        <v>-43.39033656483442</v>
       </c>
       <c r="F97">
-        <v>-3.24362016230667</v>
+        <v>-4.64341776547715</v>
       </c>
       <c r="G97">
-        <v>-11.06279158943115</v>
+        <v>-15.06843747812818</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.034958007261199</v>
       </c>
       <c r="E98">
-        <v>-41.56520983586401</v>
+        <v>-44.78224003515003</v>
       </c>
       <c r="F98">
-        <v>-3.4411998701202</v>
+        <v>-4.586406207346878</v>
       </c>
       <c r="G98">
-        <v>-11.17217863513975</v>
+        <v>-14.92344220459919</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.099911853742888</v>
       </c>
       <c r="E99">
-        <v>-43.30480954048856</v>
+        <v>-46.35260160915993</v>
       </c>
       <c r="F99">
-        <v>-3.573866223148152</v>
+        <v>-4.716120258951252</v>
       </c>
       <c r="G99">
-        <v>-11.24815234472049</v>
+        <v>-15.4274247600429</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.156973620195404</v>
       </c>
       <c r="E100">
-        <v>-45.35668149149703</v>
+        <v>-47.83585572139527</v>
       </c>
       <c r="F100">
-        <v>-3.772763863499536</v>
+        <v>-5.067891446754479</v>
       </c>
       <c r="G100">
-        <v>-11.70716279428598</v>
+        <v>-15.75015991302983</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.191786832826672</v>
       </c>
       <c r="E101">
-        <v>-47.21943304676017</v>
+        <v>-49.44609956599071</v>
       </c>
       <c r="F101">
-        <v>-3.867249106197653</v>
+        <v>-5.127335919946774</v>
       </c>
       <c r="G101">
-        <v>-12.12818142324279</v>
+        <v>-15.66580059159813</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.199910904098286</v>
       </c>
       <c r="E102">
-        <v>-49.46036539123337</v>
+        <v>-51.56413705072526</v>
       </c>
       <c r="F102">
-        <v>-4.01079109485696</v>
+        <v>-5.15498351038261</v>
       </c>
       <c r="G102">
-        <v>-12.19822925630823</v>
+        <v>-15.73160099473668</v>
       </c>
     </row>
   </sheetData>
